--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -4242,7 +4242,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -4242,7 +4242,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -4242,7 +4242,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -4242,7 +4242,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -4242,7 +4242,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -4242,7 +4242,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -4242,7 +4242,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -4242,7 +4242,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251028_201552.xlsx
@@ -4242,7 +4242,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
